--- a/files/九龙-佐敦-高临.xlsx
+++ b/files/九龙-佐敦-高临.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -703,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -749,7 +615,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -795,7 +661,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -841,7 +707,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -887,7 +753,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -933,7 +799,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -979,7 +845,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1025,7 +891,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1071,7 +937,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1117,7 +983,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1163,7 +1029,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1209,7 +1075,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1255,7 +1121,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1301,7 +1167,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1347,7 +1213,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1393,7 +1259,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1439,7 +1305,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1485,7 +1351,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1577,7 +1443,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1623,7 +1489,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1669,7 +1535,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1715,7 +1581,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1761,7 +1627,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1807,7 +1673,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1853,7 +1719,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1899,7 +1765,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1945,7 +1811,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -1991,7 +1857,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2037,7 +1903,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2129,7 +1995,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2175,7 +2041,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2221,7 +2087,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2267,7 +2133,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2313,7 +2179,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2359,7 +2225,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2451,7 +2317,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2497,7 +2363,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2543,7 +2409,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2589,7 +2455,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2635,7 +2501,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2681,7 +2547,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2727,7 +2593,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2773,7 +2639,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2819,7 +2685,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2865,7 +2731,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2911,7 +2777,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2957,7 +2823,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3003,7 +2869,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3049,7 +2915,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3095,7 +2961,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3141,7 +3007,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3187,7 +3053,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3233,7 +3099,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3279,7 +3145,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3325,7 +3191,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3371,7 +3237,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3417,7 +3283,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3463,7 +3329,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3509,7 +3375,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3555,7 +3421,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3601,7 +3467,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3647,7 +3513,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3693,7 +3559,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3739,7 +3605,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3785,7 +3651,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3831,7 +3697,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3877,7 +3743,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3923,7 +3789,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3969,7 +3835,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4015,7 +3881,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4061,7 +3927,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4107,7 +3973,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4153,7 +4019,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4199,7 +4065,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4245,7 +4111,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4337,7 +4203,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4383,7 +4249,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4429,7 +4295,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4475,7 +4341,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4521,7 +4387,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4613,7 +4479,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4659,7 +4525,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4705,7 +4571,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4751,7 +4617,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4797,7 +4663,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4843,7 +4709,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4889,7 +4755,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4935,7 +4801,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -4981,7 +4847,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5027,7 +4893,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5073,7 +4939,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5119,7 +4985,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5165,7 +5031,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5211,7 +5077,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5257,7 +5123,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5303,7 +5169,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5349,7 +5215,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5395,7 +5261,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5441,7 +5307,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5487,7 +5353,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5533,7 +5399,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5579,7 +5445,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5625,7 +5491,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5671,7 +5537,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5717,7 +5583,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5763,7 +5629,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5809,7 +5675,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5855,7 +5721,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5901,7 +5767,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -5947,7 +5813,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -5993,7 +5859,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6039,7 +5905,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6085,7 +5951,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6131,7 +5997,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6177,7 +6043,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6223,7 +6089,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6269,7 +6135,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6315,7 +6181,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6361,7 +6227,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6407,7 +6273,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6453,7 +6319,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6499,7 +6365,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6595,7 +6461,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6641,7 +6507,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6687,7 +6553,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6733,7 +6599,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6779,7 +6645,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6825,7 +6691,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6871,7 +6737,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6917,7 +6783,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -6963,7 +6829,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7009,7 +6875,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7055,7 +6921,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7101,7 +6967,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7147,7 +7013,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7193,7 +7059,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7239,7 +7105,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7285,7 +7151,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7331,7 +7197,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7377,7 +7243,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7423,7 +7289,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7469,7 +7335,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7515,7 +7381,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7561,7 +7427,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7607,7 +7473,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7653,7 +7519,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7699,7 +7565,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7745,7 +7611,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7791,7 +7657,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7837,7 +7703,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7883,7 +7749,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -7929,7 +7795,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -7975,7 +7841,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8021,7 +7887,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8067,7 +7933,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8113,7 +7979,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8159,7 +8025,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8205,7 +8071,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8251,7 +8117,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8297,7 +8163,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8343,7 +8209,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8389,7 +8255,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8481,7 +8347,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8527,7 +8393,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8573,7 +8439,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8619,7 +8485,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -8665,7 +8531,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -8711,7 +8577,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8757,7 +8623,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -8803,7 +8669,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -8849,7 +8715,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -8895,7 +8761,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -8941,7 +8807,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -8987,7 +8853,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9033,7 +8899,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9079,7 +8945,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9125,7 +8991,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -9171,7 +9037,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -9217,7 +9083,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -9263,7 +9129,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -9309,7 +9175,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -9355,7 +9221,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -9401,7 +9267,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9447,7 +9313,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -9493,7 +9359,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -9539,7 +9405,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9585,7 +9451,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -9631,7 +9497,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -9677,7 +9543,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -9723,7 +9589,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -9769,7 +9635,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -9815,7 +9681,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -9861,7 +9727,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -9907,7 +9773,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -9953,7 +9819,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -9999,7 +9865,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -10045,7 +9911,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -10091,7 +9957,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -10137,7 +10003,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -10183,7 +10049,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -10229,7 +10095,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -10275,7 +10141,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10321,7 +10187,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10367,7 +10233,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -10413,7 +10279,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -10459,7 +10325,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -10505,7 +10371,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -10551,7 +10417,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -10597,7 +10463,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -10643,7 +10509,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -10689,7 +10555,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -10735,7 +10601,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -10781,7 +10647,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -10827,7 +10693,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -10873,7 +10739,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -10919,7 +10785,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -10965,7 +10831,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11011,7 +10877,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -11057,7 +10923,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11103,7 +10969,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -11149,7 +11015,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -11195,7 +11061,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -11241,7 +11107,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -11287,7 +11153,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -11333,7 +11199,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -11379,7 +11245,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -11425,7 +11291,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -11471,7 +11337,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -11517,7 +11383,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -11563,7 +11429,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -11609,7 +11475,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -11655,7 +11521,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -11701,7 +11567,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -11747,7 +11613,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -11793,7 +11659,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -11839,7 +11705,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -11885,7 +11751,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -11931,7 +11797,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -11977,7 +11843,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -12023,7 +11889,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -12069,7 +11935,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -12115,7 +11981,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -12161,7 +12027,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -12207,7 +12073,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -12253,7 +12119,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -12299,7 +12165,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -12345,7 +12211,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -12391,7 +12257,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -12437,7 +12303,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -12483,7 +12349,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -12529,7 +12395,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -12575,7 +12441,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -12597,2667 +12463,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>高临 - A1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>122 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>122 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1589呎 (4+房)
-$6,477万
-$40,760/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 374呎 (2房)
-$827万
-$22,123/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 272呎 (1房)
-$610万
-$22,415/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 385呎 (2房)
-$886万
-$23,016/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="inlineStr"/>
-      <c r="J6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1106呎 (3房)
-$3,705万
-$33,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 1109呎 (3房)
-$3,399万
-$30,649/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 374呎 (2房)
-$820万
-$21,912/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 272呎 (1房)
-$594万
-$21,835/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 385呎 (2房)
-$872万
-$22,652/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr"/>
-      <c r="J7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 707呎 (3房)
-$1,995万
-$28,219/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$1,080万
-$25,957/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,044万
-$25,210/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,855万
-$29,728/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 378呎 (2房)
-$826万
-$21,841/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 272呎 (1房)
-$583万
-$21,423/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 385呎 (2房)
-$853万
-$22,164/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr"/>
-      <c r="J8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 707呎 (3房)
-$1,984万
-$28,066/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$1,080万
-$25,957/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,044万
-$25,210/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,897万
-$30,397/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 378呎 (2房)
-$830万
-$21,947/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 272呎 (1房)
-$566万
-$20,809/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 385呎 (2房)
-$837万
-$21,732/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr"/>
-      <c r="J9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 707呎 (3房)
-$1,836万
-$25,972/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$1,041万
-$25,029/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,006万
-$24,302/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,664万
-$26,663/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 378呎 (2房)
-$793万
-$20,979/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 272呎 (1房)
-$566万
-$20,809/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 385呎 (2房)
-$832万
-$21,603/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr"/>
-      <c r="J10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 707呎 (3房)
-$1,986万
-$28,088/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$1,043万
-$25,065/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$987万
-$23,831/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,648万
-$26,407/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 378呎 (2房)
-$813万
-$21,508/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 272呎 (1房)
-$585万
-$21,518/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 385呎 (2房)
-$993万
-$25,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr"/>
-      <c r="J11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 707呎 (3房)
-$1,859万
-$26,289/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$975万
-$23,442/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$966万
-$23,324/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,632万
-$26,154/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 378呎 (2房)
-$772万
-$20,434/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 272呎 (1房)
-$550万
-$20,202/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 385呎 (2房)
-$986万
-$25,600/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr"/>
-      <c r="J12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 707呎 (3房)
-$1,840万
-$26,031/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$966万
-$23,209/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,012万
-$24,454/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,776万
-$28,462/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 378呎 (2房)
-$751万
-$19,876/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 272呎 (1房)
-$536万
-$19,688/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 385呎 (2房)
-$828万
-$21,501/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr"/>
-      <c r="J13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 707呎 (3房)
-$1,875万
-$26,518/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$967万
-$23,252/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$958万
-$23,143/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,600万
-$25,636/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 378呎 (2房)
-$747万
-$19,757/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 272呎 (1房)
-$532万
-$19,570/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 385呎 (2房)
-$776万
-$20,166/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr"/>
-      <c r="J14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 707呎 (3房)
-$1,778万
-$25,146/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$942万
-$22,651/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$933万
-$22,536/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,661万
-$26,622/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 378呎 (2房)
-$712万
-$18,844/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 272呎 (1房)
-$557万
-$20,463/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 385呎 (2房)
-$796万
-$20,662/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr"/>
-      <c r="J15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 707呎 (3房)
-$1,704万
-$24,095/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$979万
-$23,531/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$936万
-$22,621/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,534万
-$24,583/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 378呎 (2房)
-$709万
-$18,751/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 272呎 (1房)
-$554万
-$20,357/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 385呎 (2房)
-$789万
-$20,483/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr"/>
-      <c r="J16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 707呎 (3房)
-$1,923万
-$27,200/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$927万
-$22,293/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$929万
-$22,444/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,522万
-$24,391/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 378呎 (2房)
-$705万
-$18,661/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 272呎 (1房)
-$551万
-$20,261/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 385呎 (2房)
-$738万
-$19,171/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr"/>
-      <c r="J17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 707呎 (2房)
-$1,889万
-$26,716/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$938万
-$22,555/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$929万
-$22,444/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,693万
-$27,130/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 378呎 (2房)
-$705万
-$18,661/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 272呎 (1房)
-$551万
-$20,261/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 385呎 (2房)
-$738万
-$19,171/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr"/>
-      <c r="J18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 634呎 (3房)
-$1,506万
-$23,759/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$893万
-$21,466/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$856万
-$20,679/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,580万
-$25,321/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 278呎 (1房)
-$527万
-$18,942/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$517万
-$19,216/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$680万
-$25,015/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 269呎 (1房)
-$564万
-$20,978/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 278呎 (1房)
-$543万
-$19,522/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 634呎 (3房)
-$1,500万
-$23,664/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$859万
-$20,654/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$903万
-$21,809/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,621万
-$25,971/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 278呎 (1房)
-$495万
-$17,820/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$514万
-$19,108/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$548万
-$20,129/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 269呎 (1房)
-$531万
-$19,732/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 278呎 (1房)
-$510万
-$18,360/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 634呎 (3房)
-$1,499万
-$23,648/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$906万
-$21,776/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$899万
-$21,722/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,614万
-$25,870/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 278呎 (1房)
-$494万
-$17,752/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$484万
-$17,978/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$500万
-$18,390/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 269呎 (1房)
-$560万
-$20,810/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 278呎 (1房)
-$538万
-$19,360/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 632呎 (3房)
-$1,583万
-$25,049/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 416呎 (2房)
-$850万
-$20,428/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$843万
-$20,372/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 624呎 (3房)
-$1,543万
-$24,728/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 278呎 (1房)
-$490万
-$17,633/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$508万
-$18,866/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$497万
-$18,261/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>H | 232呎 (1房)
-$647万
-$27,892/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>J | 240呎 (1房)
-$662万
-$27,600/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>高临 - A2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>137 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>136 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 1452呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 378呎 (2房)
-$890万
-$23,548/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 377呎 (2房)
-$885万
-$23,475/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 377呎 (2房)
-$881万
-$23,366/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$684万
-$25,129/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 382呎 (2房)
-$862万
-$22,555/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1056呎 (3房)
-$3,726万
-$35,280/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$1,027万
-$24,272/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 380呎 (2房)
-$861万
-$22,650/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 377呎 (2房)
-$871万
-$23,106/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 377呎 (2房)
-$867万
-$22,995/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$597万
-$21,952/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 382呎 (2房)
-$850万
-$22,264/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 569呎 (3房)
-$1,450万
-$25,485/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 415呎 (2房)
-$985万
-$23,740/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$1,014万
-$23,960/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 382呎 (2房)
-$847万
-$22,162/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 377呎 (2房)
-$852万
-$22,613/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 377呎 (2房)
-$898万
-$23,812/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$620万
-$22,794/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 382呎 (2房)
-$872万
-$22,835/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 569呎 (3房)
-$1,416万
-$24,877/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 415呎 (2房)
-$998万
-$24,051/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$1,004万
-$23,723/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 382呎 (2房)
-$830万
-$21,728/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 377呎 (2房)
-$836万
-$22,170/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 377呎 (2房)
-$832万
-$22,064/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$579万
-$21,294/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 382呎 (2房)
-$843万
-$22,065/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 569呎 (3房)
-$1,423万
-$25,014/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 415呎 (2房)
-$932万
-$22,470/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$960万
-$22,686/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 382呎 (2房)
-$801万
-$20,974/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 377呎 (2房)
-$844万
-$22,393/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 377呎 (2房)
-$840万
-$22,286/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$559万
-$20,544/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 382呎 (2房)
-$814万
-$21,301/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 569呎 (3房)
-$1,446万
-$25,422/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 415呎 (2房)
-$958万
-$23,087/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$953万
-$22,532/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 382呎 (2房)
-$833万
-$21,804/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 377呎 (2房)
-$838万
-$22,241/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 377呎 (2房)
-$834万
-$22,133/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$588万
-$21,625/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 382呎 (2房)
-$846万
-$22,157/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 569呎 (3房)
-$1,404万
-$24,678/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 415呎 (2房)
-$941万
-$22,672/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$947万
-$22,381/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 382呎 (2房)
-$781万
-$20,450/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 377呎 (2房)
-$833万
-$22,093/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 377呎 (2房)
-$828万
-$21,976/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$705万
-$25,919/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 382呎 (2房)
-$804万
-$21,052/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 569呎 (3房)
-$1,394万
-$24,504/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 415呎 (2房)
-$913万
-$22,005/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$940万
-$22,222/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 382呎 (2房)
-$776万
-$20,306/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 377呎 (2房)
-$781万
-$20,721/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 377呎 (2房)
-$823万
-$21,825/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$581万
-$21,375/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 382呎 (2房)
-$799万
-$20,927/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 569呎 (3房)
-$1,385万
-$24,334/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 415呎 (2房)
-$907万
-$21,848/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$934万
-$22,073/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 382呎 (2房)
-$816万
-$21,351/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 377呎 (2房)
-$821万
-$21,785/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 377呎 (2房)
-$772万
-$20,472/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$546万
-$20,059/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 382呎 (2房)
-$813万
-$21,288/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 569呎 (3房)
-$1,260万
-$22,135/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 415呎 (2房)
-$901万
-$21,704/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$905万
-$21,385/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 382呎 (2房)
-$730万
-$19,097/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 377呎 (2房)
-$735万
-$19,485/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 377呎 (2房)
-$732万
-$19,430/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$527万
-$19,375/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>H | 382呎 (2房)
-$742万
-$19,419/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 569呎 (3房)
-$1,330万
-$23,374/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 415呎 (2房)
-$896万
-$21,578/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$910万
-$21,511/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 382呎 (2房)
-$725万
-$18,982/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 377呎 (2房)
-$730万
-$19,369/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 377呎 (2房)
-$771万
-$20,454/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$525万
-$19,287/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 382呎 (2房)
-$782万
-$20,458/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 569呎 (3房)
-$1,322万
-$23,239/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 415呎 (2房)
-$841万
-$20,255/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$946万
-$22,376/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 382呎 (2房)
-$974万
-$25,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 377呎 (2房)
-$726万
-$19,252/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 377呎 (2房)
-$724万
-$19,202/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$522万
-$19,184/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>H | 382呎 (2房)
-$778万
-$20,359/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 569呎 (3房)
-$1,453万
-$25,543/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 415呎 (2房)
-$841万
-$20,255/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$894万
-$21,132/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 382呎 (2房)
-$722万
-$18,914/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 377呎 (2房)
-$768万
-$20,385/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 377呎 (2房)
-$724万
-$19,202/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 272呎 (1房)
-$552万
-$20,312/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>H | 382呎 (2房)
-$734万
-$19,228/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 545呎 (3房)
-$1,159万
-$21,261/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 418呎 (2房)
-$825万
-$19,744/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$835万
-$19,740/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 277呎 (1房)
-$511万
-$18,437/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 269呎 (1房)
-$568万
-$21,104/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 270呎 (1房)
-$507万
-$18,785/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 270呎 (1房)
-$505万
-$18,715/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 272呎 (1房)
-$495万
-$18,188/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 277呎 (1房)
-$538万
-$19,404/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 545呎 (3房)
-$1,222万
-$22,424/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 418呎 (2房)
-$870万
-$20,818/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$881万
-$20,820/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 277呎 (1房)
-$538万
-$19,440/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 269呎 (1房)
-$534万
-$19,862/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 270呎 (1房)
-$535万
-$19,811/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 270呎 (1房)
-$533万
-$19,741/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 272呎 (1房)
-$492万
-$18,099/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 277呎 (1房)
-$535万
-$19,303/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 545呎 (3房)
-$1,150万
-$21,092/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 418呎 (2房)
-$819万
-$19,584/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 423呎 (2房)
-$828万
-$19,586/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 277呎 (1房)
-$536万
-$19,365/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 269呎 (1房)
-$563万
-$20,933/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 270呎 (1房)
-$503万
-$18,637/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 270呎 (1房)
-$501万
-$18,567/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 272呎 (1房)
-$519万
-$19,070/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 277呎 (1房)
-$532万
-$19,209/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 508呎 (3房)
-$1,432万
-$28,181/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 380呎 (2房)
-$1,096万
-$28,850/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 385呎 (2房)
-$1,110万
-$28,844/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 239呎 (1房)
-$638万
-$26,690/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 232呎 (1房)
-$688万
-$29,651/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 232呎 (1房)
-$618万
-$26,638/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 232呎 (1房)
-$650万
-$28,030/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>H | 272呎 (1房)
-$486万
-$17,871/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>J | 277呎 (1房)
-$499万
-$18,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-佐敦-高临.xlsx
+++ b/files/九龙-佐敦-高临.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A2座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +137,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +218,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -12463,4 +12634,2667 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>A1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1589呎 (4+房)
+$6477万
+$40,760/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 374呎 (2房)
+$827万
+$22,123/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 272呎 (1房)
+$610万
+$22,415/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 385呎 (2房)
+$886万
+$23,016/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1106呎 (3房)
+$3705万
+$33,500/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1109呎 (3房)
+$3399万
+$30,649/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 374呎 (2房)
+$820万
+$21,912/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 272呎 (1房)
+$594万
+$21,835/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 385呎 (2房)
+$872万
+$22,652/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 707呎 (3房)
+$1995万
+$28,219/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$1080万
+$25,957/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1044万
+$25,210/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1855万
+$29,728/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 378呎 (2房)
+$826万
+$21,841/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 272呎 (1房)
+$583万
+$21,423/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 385呎 (2房)
+$853万
+$22,164/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 707呎 (3房)
+$1984万
+$28,066/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$1080万
+$25,957/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1044万
+$25,210/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1897万
+$30,397/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 378呎 (2房)
+$830万
+$21,947/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 272呎 (1房)
+$566万
+$20,809/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 385呎 (2房)
+$837万
+$21,732/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr"/>
+      <c r="J8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 707呎 (3房)
+$1836万
+$25,972/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$1041万
+$25,029/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1006万
+$24,302/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1664万
+$26,663/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 378呎 (2房)
+$793万
+$20,979/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 272呎 (1房)
+$566万
+$20,809/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 385呎 (2房)
+$832万
+$21,603/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr"/>
+      <c r="J9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 707呎 (3房)
+$1986万
+$28,088/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$1043万
+$25,065/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$987万
+$23,831/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1648万
+$26,407/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 378呎 (2房)
+$813万
+$21,508/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 272呎 (1房)
+$585万
+$21,518/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 385呎 (2房)
+$993万
+$25,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr"/>
+      <c r="J10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 707呎 (3房)
+$1859万
+$26,289/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$975万
+$23,442/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$966万
+$23,324/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1632万
+$26,154/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 378呎 (2房)
+$772万
+$20,434/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 272呎 (1房)
+$550万
+$20,202/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 385呎 (2房)
+$986万
+$25,600/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr"/>
+      <c r="J11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 707呎 (3房)
+$1840万
+$26,031/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$966万
+$23,209/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1012万
+$24,454/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1776万
+$28,462/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 378呎 (2房)
+$751万
+$19,876/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 272呎 (1房)
+$536万
+$19,688/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 385呎 (2房)
+$828万
+$21,501/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr"/>
+      <c r="J12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 707呎 (3房)
+$1875万
+$26,518/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$967万
+$23,252/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$958万
+$23,143/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1600万
+$25,636/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 378呎 (2房)
+$747万
+$19,757/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 272呎 (1房)
+$532万
+$19,570/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 385呎 (2房)
+$776万
+$20,166/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 707呎 (3房)
+$1778万
+$25,146/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$942万
+$22,651/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$933万
+$22,536/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1661万
+$26,622/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 378呎 (2房)
+$712万
+$18,844/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 272呎 (1房)
+$557万
+$20,463/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 385呎 (2房)
+$796万
+$20,662/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr"/>
+      <c r="J14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 707呎 (3房)
+$1704万
+$24,095/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$979万
+$23,531/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$936万
+$22,621/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1534万
+$24,583/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 378呎 (2房)
+$709万
+$18,751/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 272呎 (1房)
+$554万
+$20,357/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 385呎 (2房)
+$789万
+$20,483/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 707呎 (3房)
+$1923万
+$27,200/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$927万
+$22,293/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$929万
+$22,444/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1522万
+$24,391/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 378呎 (2房)
+$705万
+$18,661/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 272呎 (1房)
+$551万
+$20,261/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 385呎 (2房)
+$738万
+$19,171/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr"/>
+      <c r="J16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 707呎 (2房)
+$1889万
+$26,716/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$938万
+$22,555/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$929万
+$22,444/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1693万
+$27,130/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 378呎 (2房)
+$705万
+$18,661/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 272呎 (1房)
+$551万
+$20,261/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 385呎 (2房)
+$738万
+$19,171/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr"/>
+      <c r="J17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 634呎 (3房)
+$1506万
+$23,759/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$893万
+$21,466/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$856万
+$20,679/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1580万
+$25,321/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 278呎 (1房)
+$527万
+$18,942/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$517万
+$19,216/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$680万
+$25,015/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 269呎 (1房)
+$564万
+$20,978/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$543万
+$19,522/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 634呎 (3房)
+$1500万
+$23,664/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$859万
+$20,654/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$903万
+$21,809/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1621万
+$25,971/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 278呎 (1房)
+$495万
+$17,820/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$514万
+$19,108/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$548万
+$20,129/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 269呎 (1房)
+$531万
+$19,732/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$510万
+$18,360/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 634呎 (3房)
+$1499万
+$23,648/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$906万
+$21,776/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$899万
+$21,722/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1614万
+$25,870/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 278呎 (1房)
+$494万
+$17,752/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$484万
+$17,978/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$500万
+$18,390/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 269呎 (1房)
+$560万
+$20,810/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$538万
+$19,360/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 632呎 (3房)
+$1583万
+$25,049/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 416呎 (2房)
+$850万
+$20,428/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$843万
+$20,372/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 624呎 (3房)
+$1543万
+$24,728/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 278呎 (1房)
+$490万
+$17,633/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$508万
+$18,866/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$497万
+$18,261/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 232呎 (1房)
+$647万
+$27,892/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 240呎 (1房)
+$662万
+$27,600/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>A2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 1452呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$890万
+$23,548/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 377呎 (2房)
+$885万
+$23,475/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 377呎 (2房)
+$881万
+$23,366/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$684万
+$25,129/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 382呎 (2房)
+$862万
+$22,555/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1056呎 (3房)
+$3726万
+$35,280/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$1027万
+$24,272/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 380呎 (2房)
+$861万
+$22,650/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 377呎 (2房)
+$871万
+$23,106/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 377呎 (2房)
+$867万
+$22,995/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$597万
+$21,952/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 382呎 (2房)
+$850万
+$22,264/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 569呎 (3房)
+$1450万
+$25,485/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 415呎 (2房)
+$985万
+$23,740/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$1014万
+$23,960/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 382呎 (2房)
+$847万
+$22,162/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 377呎 (2房)
+$852万
+$22,613/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 377呎 (2房)
+$898万
+$23,812/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$620万
+$22,794/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 382呎 (2房)
+$872万
+$22,835/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 569呎 (3房)
+$1416万
+$24,877/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 415呎 (2房)
+$998万
+$24,051/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$1004万
+$23,723/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 382呎 (2房)
+$830万
+$21,728/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 377呎 (2房)
+$836万
+$22,170/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 377呎 (2房)
+$832万
+$22,064/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$579万
+$21,294/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 382呎 (2房)
+$843万
+$22,065/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 569呎 (3房)
+$1423万
+$25,014/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 415呎 (2房)
+$932万
+$22,470/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$960万
+$22,686/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 382呎 (2房)
+$801万
+$20,974/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 377呎 (2房)
+$844万
+$22,393/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 377呎 (2房)
+$840万
+$22,286/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$559万
+$20,544/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 382呎 (2房)
+$814万
+$21,301/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 569呎 (3房)
+$1446万
+$25,422/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 415呎 (2房)
+$958万
+$23,087/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$953万
+$22,532/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 382呎 (2房)
+$833万
+$21,804/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 377呎 (2房)
+$838万
+$22,241/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 377呎 (2房)
+$834万
+$22,133/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$588万
+$21,625/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 382呎 (2房)
+$846万
+$22,157/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 569呎 (3房)
+$1404万
+$24,678/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 415呎 (2房)
+$941万
+$22,672/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$947万
+$22,381/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 382呎 (2房)
+$781万
+$20,450/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 377呎 (2房)
+$833万
+$22,093/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 377呎 (2房)
+$828万
+$21,976/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$705万
+$25,919/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 382呎 (2房)
+$804万
+$21,052/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 569呎 (3房)
+$1394万
+$24,504/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 415呎 (2房)
+$913万
+$22,005/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$940万
+$22,222/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 382呎 (2房)
+$776万
+$20,306/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 377呎 (2房)
+$781万
+$20,721/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 377呎 (2房)
+$823万
+$21,825/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$581万
+$21,375/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 382呎 (2房)
+$799万
+$20,927/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 569呎 (3房)
+$1385万
+$24,334/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 415呎 (2房)
+$907万
+$21,848/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$934万
+$22,073/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 382呎 (2房)
+$816万
+$21,351/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 377呎 (2房)
+$821万
+$21,785/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 377呎 (2房)
+$772万
+$20,472/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$546万
+$20,059/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 382呎 (2房)
+$813万
+$21,288/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 569呎 (3房)
+$1260万
+$22,135/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 415呎 (2房)
+$901万
+$21,704/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$905万
+$21,385/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 382呎 (2房)
+$730万
+$19,097/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 377呎 (2房)
+$735万
+$19,485/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 377呎 (2房)
+$732万
+$19,430/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$527万
+$19,375/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 382呎 (2房)
+$742万
+$19,419/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 569呎 (3房)
+$1330万
+$23,374/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 415呎 (2房)
+$896万
+$21,578/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$910万
+$21,511/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 382呎 (2房)
+$725万
+$18,982/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 377呎 (2房)
+$730万
+$19,369/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 377呎 (2房)
+$771万
+$20,454/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$525万
+$19,287/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 382呎 (2房)
+$782万
+$20,458/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 569呎 (3房)
+$1322万
+$23,239/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 415呎 (2房)
+$841万
+$20,255/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$946万
+$22,376/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 382呎 (2房)
+$974万
+$25,500/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 377呎 (2房)
+$726万
+$19,252/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 377呎 (2房)
+$724万
+$19,202/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$522万
+$19,184/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 382呎 (2房)
+$778万
+$20,359/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 569呎 (3房)
+$1453万
+$25,543/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 415呎 (2房)
+$841万
+$20,255/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$894万
+$21,132/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 382呎 (2房)
+$722万
+$18,914/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 377呎 (2房)
+$768万
+$20,385/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 377呎 (2房)
+$724万
+$19,202/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 272呎 (1房)
+$552万
+$20,312/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 382呎 (2房)
+$734万
+$19,228/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 545呎 (3房)
+$1159万
+$21,261/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 418呎 (2房)
+$825万
+$19,744/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$835万
+$19,740/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 277呎 (1房)
+$511万
+$18,437/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 269呎 (1房)
+$568万
+$21,104/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 270呎 (1房)
+$507万
+$18,785/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 270呎 (1房)
+$505万
+$18,715/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 272呎 (1房)
+$495万
+$18,188/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 277呎 (1房)
+$538万
+$19,404/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 545呎 (3房)
+$1222万
+$22,424/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 418呎 (2房)
+$870万
+$20,818/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$881万
+$20,820/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 277呎 (1房)
+$538万
+$19,440/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 269呎 (1房)
+$534万
+$19,862/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 270呎 (1房)
+$535万
+$19,811/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 270呎 (1房)
+$533万
+$19,741/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 272呎 (1房)
+$492万
+$18,099/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 277呎 (1房)
+$535万
+$19,303/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 545呎 (3房)
+$1150万
+$21,092/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 418呎 (2房)
+$819万
+$19,584/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 423呎 (2房)
+$828万
+$19,586/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 277呎 (1房)
+$536万
+$19,365/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 269呎 (1房)
+$563万
+$20,933/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 270呎 (1房)
+$503万
+$18,637/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 270呎 (1房)
+$501万
+$18,567/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 272呎 (1房)
+$519万
+$19,070/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 277呎 (1房)
+$532万
+$19,209/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 508呎 (3房)
+$1432万
+$28,181/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 380呎 (2房)
+$1096万
+$28,850/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 385呎 (2房)
+$1110万
+$28,844/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 239呎 (1房)
+$638万
+$26,690/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 232呎 (1房)
+$688万
+$29,651/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 232呎 (1房)
+$618万
+$26,638/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 232呎 (1房)
+$650万
+$28,030/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 272呎 (1房)
+$486万
+$17,871/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 277呎 (1房)
+$499万
+$18,000/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-佐敦-高临.xlsx
+++ b/files/九龙-佐敦-高临.xlsx
@@ -645,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-佐敦-高临.xlsx
+++ b/files/九龙-佐敦-高临.xlsx
@@ -122,7 +122,7 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -267,7 +267,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J261"/>
+  <dimension ref="A1:N261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -648,6 +648,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -705,6 +709,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -751,6 +775,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>8861000</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>23016</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -797,6 +837,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>6097000</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>22415</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -843,6 +899,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>8274000</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>22123</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -889,6 +961,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>64768000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>40760</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -935,6 +1023,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>8721000</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>22652</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -981,6 +1085,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>5939000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>21835</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1027,6 +1147,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>8195000</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>21912</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1073,6 +1209,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>33990000</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>30649</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1119,6 +1271,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>37051000</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>33500</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1165,6 +1333,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>8533000</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>22164</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1211,6 +1395,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>5827000</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>21423</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1257,6 +1457,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>8256000</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>21841</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1303,6 +1519,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>18550272</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>29728</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1349,6 +1581,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>10437000</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>25210</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1395,6 +1643,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>10798000</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>25957</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1441,6 +1705,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>19951000</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>28219</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1487,6 +1767,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>8367000</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>21732</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1533,6 +1829,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>5660000</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>20809</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1579,6 +1891,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>8296000</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>21947</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1625,6 +1953,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>18968000</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>30397</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1671,6 +2015,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>10437000</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>25210</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1717,6 +2077,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>10798000</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>25957</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1763,6 +2139,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>19843000</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>28066</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1809,6 +2201,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>8317000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>21603</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1855,6 +2263,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>5660000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>20809</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1901,6 +2325,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>7930000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>20979</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1947,6 +2387,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>16638000</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>26663</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1993,6 +2449,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>10061000</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>24302</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2039,6 +2511,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>10412000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>25029</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2085,6 +2573,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>18362000</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>25972</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2120,7 +2624,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2131,6 +2635,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>9933000</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>25800</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2177,6 +2697,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>5853000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>21518</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2223,6 +2759,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>8130000</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>21508</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2269,6 +2821,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>16478000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>26407</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2315,6 +2883,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>9866000</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>23831</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2361,6 +2945,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>10427000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>25065</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2407,6 +3007,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>19858000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>28088</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2442,7 +3058,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2453,6 +3069,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>9856000</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>25600</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2499,6 +3131,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>5495000</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>20202</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2545,6 +3193,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>7724000</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>20434</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2591,6 +3255,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>16320000</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>26154</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2637,6 +3317,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>9656000</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>23324</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2683,6 +3379,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>9752000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>23442</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2729,6 +3441,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>18586000</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>26289</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2775,6 +3503,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>8278000</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>21501</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2821,6 +3565,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>5355000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>19688</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2867,6 +3627,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>7513000</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>19876</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2913,6 +3689,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>17760000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>28462</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2959,6 +3751,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>10124000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>24454</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3005,6 +3813,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>9655000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>23209</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3051,6 +3875,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>18404000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>26031</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3097,6 +3937,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>7764000</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>20166</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3143,6 +3999,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>5323000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>19570</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3189,6 +4061,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>7468000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>19757</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3235,6 +4123,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>15997000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>25636</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3281,6 +4185,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>9581000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>23143</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3327,6 +4247,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>9673000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>23252</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3373,6 +4309,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>18748000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>26518</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3419,6 +4371,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>7955000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>20662</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3465,6 +4433,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>5566000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>20463</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3511,6 +4495,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>7123000</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>18844</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3557,6 +4557,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>16612000</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>26622</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3603,6 +4619,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>9330000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>22536</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3649,6 +4681,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>9423000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>22651</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3695,6 +4743,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>17778000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>25146</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3741,6 +4805,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>7886000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>20483</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3787,6 +4867,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>5537000</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>20357</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3833,6 +4929,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>7088000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>18751</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3879,6 +4991,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>15340000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>24583</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3925,6 +5053,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>9365000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>22621</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3971,6 +5115,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>9789000</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>23531</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4017,6 +5177,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>17035000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>24095</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4063,6 +5239,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>7381000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>19171</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4109,6 +5301,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>5511000</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>20261</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4155,6 +5363,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>7054000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>18661</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4201,6 +5425,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>15220000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>24391</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4247,6 +5487,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>9292000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>22444</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4293,6 +5549,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>9274000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>22293</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4328,7 +5600,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4339,6 +5611,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>19230400</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>27200</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4385,6 +5673,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>7381000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>19171</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4431,6 +5735,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>5511000</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>20261</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4477,6 +5797,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>7054000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>18661</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4523,6 +5859,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>16929000</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>27130</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4569,6 +5921,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>9292000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>22444</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4615,6 +5983,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>9383000</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>22555</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4661,6 +6045,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>18888000</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>26716</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4707,6 +6107,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>5427000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>19522</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4753,6 +6169,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>5643000</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>20978</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4799,6 +6231,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>6804000</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>25015</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4845,6 +6293,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>5169000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>19216</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4891,6 +6355,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>5266000</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>18942</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4937,6 +6417,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>15800000</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>25321</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4983,6 +6479,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>8561000</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>20679</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5029,6 +6541,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>8930000</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>21466</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5075,6 +6603,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>15063000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>23759</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5121,6 +6665,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>5104000</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>18360</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5167,6 +6727,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>5308000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>19732</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5213,6 +6789,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>5475000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>20129</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5259,6 +6851,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>5140000</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>19108</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5305,6 +6913,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>4954000</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>17820</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5351,6 +6975,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>16206000</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>25971</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5397,6 +7037,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>9029000</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>21809</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5443,6 +7099,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>8592000</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>20654</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5489,6 +7161,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>15003000</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>23664</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5535,6 +7223,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>5382000</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>19360</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5581,6 +7285,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>5598000</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>20810</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5627,6 +7347,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>5002000</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>18390</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5673,6 +7409,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>4836000</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>17978</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5719,6 +7471,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>4935000</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>17752</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5765,6 +7533,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>16143000</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>25870</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5811,6 +7595,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>8993000</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>21722</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5857,6 +7657,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>9059000</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>21776</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5903,6 +7719,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>14993000</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>23648</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5949,6 +7781,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>6624000</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>27600</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5995,6 +7843,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>6471000</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>27892</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6041,6 +7905,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>4967000</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>18261</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6087,6 +7967,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>5075000</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>18866</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6133,6 +8029,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>4902000</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>17633</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6179,6 +8091,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>15430000</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>24728</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6225,6 +8153,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>8434000</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>20372</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6271,6 +8215,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>8498000</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>20428</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6317,6 +8277,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>15831000</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>25049</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6363,6 +8339,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>8616000</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>22555</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6409,6 +8401,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>6835000</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>25129</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6455,6 +8463,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>8809000</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>23366</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6501,6 +8525,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>8850000</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>23475</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6547,6 +8587,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>8901000</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>23548</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6577,7 +8633,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -6587,17 +8643,37 @@
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6643,6 +8719,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>8505000</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>22264</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6689,6 +8781,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>5971000</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>21952</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6735,6 +8843,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>8669000</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>22995</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6781,6 +8905,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>8711000</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>23106</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6827,6 +8967,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>8607000</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>22650</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6873,6 +9029,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>10267000</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>24272</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6919,6 +9091,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>37255680</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>35280</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6965,6 +9153,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>8723000</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>22835</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7011,6 +9215,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>22794</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7057,6 +9277,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>8977000</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>23812</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7103,6 +9339,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>8525000</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>22613</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7149,6 +9401,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>8466000</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>22162</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7195,6 +9463,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>10135000</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>23960</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7241,6 +9525,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>9852000</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>23740</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7287,6 +9587,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>14501000</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>25485</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7333,6 +9649,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>8429000</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>22065</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7379,6 +9711,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>5792000</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>21294</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7425,6 +9773,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>8318000</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>22064</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7471,6 +9835,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>8358000</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>22170</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7517,6 +9897,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>8300000</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>21728</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7563,6 +9959,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>10035000</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>23723</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7609,6 +10021,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>9981000</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>24051</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7655,6 +10083,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>14155000</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>24877</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7701,6 +10145,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>8137000</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>21301</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7747,6 +10207,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>5588000</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>20544</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7793,6 +10269,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>8402000</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>22286</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7839,6 +10331,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>8442000</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>22393</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7885,6 +10393,22 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>8012000</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>20974</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7931,6 +10455,22 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>9596000</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>22686</v>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7977,6 +10517,22 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>9325000</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>22470</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8023,6 +10579,22 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>14233000</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>25014</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8069,6 +10641,22 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>8464000</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>22157</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8115,6 +10703,22 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>5882000</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>21625</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8161,6 +10765,22 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>8344000</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>22133</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8207,6 +10827,22 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>8385000</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>22241</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8253,6 +10889,22 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>8329000</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>21804</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8299,6 +10951,22 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>9531000</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>22532</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8345,6 +11013,22 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>9581000</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>23087</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8391,6 +11075,22 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>14465000</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>25422</v>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8437,6 +11137,22 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>8042000</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>21052</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8483,6 +11199,22 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>7050000</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>25919</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8529,6 +11261,22 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>8285000</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>21976</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8575,6 +11323,22 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>8329000</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>22093</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8621,6 +11385,22 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>7812000</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>20450</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8667,6 +11447,22 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>9467000</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>22381</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8713,6 +11509,22 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>9409000</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>22672</v>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8759,6 +11571,22 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>14042000</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>24678</v>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8805,6 +11633,22 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>7994000</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>20927</v>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8851,6 +11695,22 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>5814000</v>
+      </c>
+      <c r="L179" s="5" t="n">
+        <v>21375</v>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8897,6 +11757,22 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>8228000</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>21825</v>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8943,6 +11819,22 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>7812000</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>20721</v>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8989,6 +11881,22 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>7757000</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>20306</v>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9035,6 +11943,22 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>9400000</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>22222</v>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9081,6 +12005,22 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>9132000</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>22005</v>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9127,6 +12067,22 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>13943000</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>24504</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9173,6 +12129,22 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>8132000</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>21288</v>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9219,6 +12191,22 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>5456000</v>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>20059</v>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9265,6 +12253,22 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>7718000</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>20472</v>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9311,6 +12315,22 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>8213000</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>21785</v>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9357,6 +12377,22 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>8156000</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>21351</v>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9403,6 +12439,22 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>9337000</v>
+      </c>
+      <c r="L191" s="5" t="n">
+        <v>22073</v>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9449,6 +12501,22 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>9067000</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>21848</v>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9495,6 +12563,22 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>13846000</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>24334</v>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9541,6 +12625,22 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>7418000</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>19419</v>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9587,6 +12687,22 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>5270000</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>19375</v>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9633,6 +12749,22 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>7325000</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>19430</v>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9679,6 +12811,22 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>7346000</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>19485</v>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9725,6 +12873,22 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>7295000</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>19097</v>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9771,6 +12935,22 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>9046000</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>21385</v>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9817,6 +12997,22 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>9007000</v>
+      </c>
+      <c r="L200" s="5" t="n">
+        <v>21704</v>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9863,6 +13059,22 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>12595000</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>22135</v>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9909,6 +13121,22 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>7815000</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>20458</v>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9955,6 +13183,22 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>5246000</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>19287</v>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10001,6 +13245,22 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>7711000</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>20454</v>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10047,6 +13307,22 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>7302000</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>19369</v>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10093,6 +13369,22 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>7251000</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>18982</v>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10139,6 +13431,22 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>9099000</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>21511</v>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10185,6 +13493,22 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="n">
+        <v>8955000</v>
+      </c>
+      <c r="L208" s="5" t="n">
+        <v>21578</v>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10231,6 +13555,22 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>13300000</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>23374</v>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10277,6 +13617,22 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>7777000</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>20359</v>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10323,6 +13679,22 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>5218000</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>19184</v>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10369,6 +13741,22 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>7239000</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>19202</v>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10415,6 +13803,22 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>7258000</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>19252</v>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10461,6 +13865,22 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>9741000</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>25500</v>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10507,6 +13927,22 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>9465000</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>22376</v>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10553,6 +13989,22 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>8406000</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>20255</v>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10599,6 +14051,22 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="5" t="n">
+        <v>13223000</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>23239</v>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10645,6 +14113,22 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>7345000</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>19228</v>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10691,6 +14175,22 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="5" t="n">
+        <v>5525000</v>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>20312</v>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10737,6 +14237,22 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="5" t="n">
+        <v>7239000</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>19202</v>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10783,6 +14299,22 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>7685000</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>20385</v>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10829,6 +14361,22 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>7225000</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>18914</v>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10875,6 +14423,22 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>8939000</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>21132</v>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10921,6 +14485,22 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>8406000</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>20255</v>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10967,6 +14547,22 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>14534000</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>25543</v>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11013,6 +14609,22 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>5375000</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>19404</v>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11059,6 +14671,22 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>4947000</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>18188</v>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11105,6 +14733,22 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>5053000</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>18715</v>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11151,6 +14795,22 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>5072000</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>18785</v>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11197,6 +14857,22 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>5677000</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>21104</v>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11243,6 +14919,22 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>5107000</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>18437</v>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11289,6 +14981,22 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>8350000</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>19740</v>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11335,6 +15043,22 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>8253000</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>19744</v>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11381,6 +15105,22 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>11587000</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>21261</v>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11427,6 +15167,22 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>5347000</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>19303</v>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11473,6 +15229,22 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>4923000</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>18099</v>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11519,6 +15291,22 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>5330000</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>19741</v>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11565,6 +15353,22 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" s="5" t="n">
+        <v>5349000</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>19811</v>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11611,6 +15415,22 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>5343000</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>19862</v>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11657,6 +15477,22 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>5385000</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>19440</v>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11703,6 +15539,22 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>8807000</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>20820</v>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11749,6 +15601,22 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>8702000</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>20818</v>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11795,6 +15663,22 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" s="5" t="n">
+        <v>12221000</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>22424</v>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11841,6 +15725,22 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" s="5" t="n">
+        <v>5321000</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>19209</v>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11887,6 +15787,22 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="n">
+        <v>5187000</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>19070</v>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11933,6 +15849,22 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" s="5" t="n">
+        <v>5013000</v>
+      </c>
+      <c r="L246" s="5" t="n">
+        <v>18567</v>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11979,6 +15911,22 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>5032000</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>18637</v>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12025,6 +15973,22 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>5631000</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>20933</v>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12071,6 +16035,22 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>5364000</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>19365</v>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12117,6 +16097,22 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>8285000</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>19586</v>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12163,6 +16159,22 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" s="5" t="n">
+        <v>8186000</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>19584</v>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12209,6 +16221,22 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" s="5" t="n">
+        <v>11495000</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>21092</v>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12255,6 +16283,22 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" s="5" t="n">
+        <v>4986000</v>
+      </c>
+      <c r="L253" s="5" t="n">
+        <v>18000</v>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12301,6 +16345,22 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>4861000</v>
+      </c>
+      <c r="L254" s="5" t="n">
+        <v>17871</v>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12347,6 +16407,22 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="5" t="n">
+        <v>6503000</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>28030</v>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12393,6 +16469,22 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>6180000</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>26638</v>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12439,6 +16531,22 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="n">
+        <v>6879000</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>29651</v>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12485,6 +16593,22 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" s="5" t="n">
+        <v>6379000</v>
+      </c>
+      <c r="L258" s="5" t="n">
+        <v>26690</v>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12531,6 +16655,22 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" s="5" t="n">
+        <v>11105000</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>28844</v>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12577,6 +16717,22 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>10963000</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>28850</v>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12623,13 +16779,29 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" s="5" t="n">
+        <v>14316000</v>
+      </c>
+      <c r="L261" s="5" t="n">
+        <v>28181</v>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -12791,7 +16963,7 @@
           <t>A | 1589呎 (4+房)
 $6477万
 $40,760/呎
-(24年-10月)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -12802,7 +16974,7 @@
           <t>E | 374呎 (2房)
 $827万
 $22,123/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -12810,7 +16982,7 @@
           <t>F | 272呎 (1房)
 $610万
 $22,415/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -12818,7 +16990,7 @@
           <t>G | 385呎 (2房)
 $886万
 $23,016/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="I5" s="21" t="inlineStr"/>
@@ -12835,7 +17007,7 @@
           <t>A | 1106呎 (3房)
 $3705万
 $33,500/呎
-(24年-12月)</t>
+(24年-12月-26日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -12843,7 +17015,7 @@
           <t>B | 1109呎 (3房)
 $3399万
 $30,649/呎
-(24年-06月)</t>
+(24年-06月-18日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -12853,7 +17025,7 @@
           <t>E | 374呎 (2房)
 $820万
 $21,912/呎
-(25年-05月)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -12861,7 +17033,7 @@
           <t>F | 272呎 (1房)
 $594万
 $21,835/呎
-(24年-09月)</t>
+(24年-09月-12日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -12869,7 +17041,7 @@
           <t>G | 385呎 (2房)
 $872万
 $22,652/呎
-(25年-06月)</t>
+(25年-06月-08日)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr"/>
@@ -12886,7 +17058,7 @@
           <t>A | 707呎 (3房)
 $1995万
 $28,219/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -12894,7 +17066,7 @@
           <t>B | 416呎 (2房)
 $1080万
 $25,957/呎
-(24年-12月)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -12902,7 +17074,7 @@
           <t>C | 414呎 (2房)
 $1044万
 $25,210/呎
-(25年-04月)</t>
+(25年-04月-27日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -12910,7 +17082,7 @@
           <t>D | 624呎 (3房)
 $1855万
 $29,728/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -12918,7 +17090,7 @@
           <t>E | 378呎 (2房)
 $826万
 $21,841/呎
-(25年-05月)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -12926,7 +17098,7 @@
           <t>F | 272呎 (1房)
 $583万
 $21,423/呎
-(24年-09月)</t>
+(24年-09月-12日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -12934,7 +17106,7 @@
           <t>G | 385呎 (2房)
 $853万
 $22,164/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr"/>
@@ -12951,7 +17123,7 @@
           <t>A | 707呎 (3房)
 $1984万
 $28,066/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -12959,7 +17131,7 @@
           <t>B | 416呎 (2房)
 $1080万
 $25,957/呎
-(24年-12月)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -12967,7 +17139,7 @@
           <t>C | 414呎 (2房)
 $1044万
 $25,210/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -12975,7 +17147,7 @@
           <t>D | 624呎 (3房)
 $1897万
 $30,397/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -12983,7 +17155,7 @@
           <t>E | 378呎 (2房)
 $830万
 $21,947/呎
-(25年-01月)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -12991,7 +17163,7 @@
           <t>F | 272呎 (1房)
 $566万
 $20,809/呎
-(24年-07月)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -12999,7 +17171,7 @@
           <t>G | 385呎 (2房)
 $837万
 $21,732/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr"/>
@@ -13016,7 +17188,7 @@
           <t>A | 707呎 (3房)
 $1836万
 $25,972/呎
-(24年-06月)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -13024,7 +17196,7 @@
           <t>B | 416呎 (2房)
 $1041万
 $25,029/呎
-(25年-01月)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -13032,7 +17204,7 @@
           <t>C | 414呎 (2房)
 $1006万
 $24,302/呎
-(25年-04月)</t>
+(25年-04月-27日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -13040,7 +17212,7 @@
           <t>D | 624呎 (3房)
 $1664万
 $26,663/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -13048,7 +17220,7 @@
           <t>E | 378呎 (2房)
 $793万
 $20,979/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -13056,7 +17228,7 @@
           <t>F | 272呎 (1房)
 $566万
 $20,809/呎
-(24年-07月)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -13064,7 +17236,7 @@
           <t>G | 385呎 (2房)
 $832万
 $21,603/呎
-(24年-08月)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr"/>
@@ -13081,7 +17253,7 @@
           <t>A | 707呎 (3房)
 $1986万
 $28,088/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -13089,7 +17261,7 @@
           <t>B | 416呎 (2房)
 $1043万
 $25,065/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -13097,7 +17269,7 @@
           <t>C | 414呎 (2房)
 $987万
 $23,831/呎
-(25年-04月)</t>
+(25年-04月-13日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -13105,7 +17277,7 @@
           <t>D | 624呎 (3房)
 $1648万
 $26,407/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -13113,7 +17285,7 @@
           <t>E | 378呎 (2房)
 $813万
 $21,508/呎
-(24年-07月)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -13121,7 +17293,7 @@
           <t>F | 272呎 (1房)
 $585万
 $21,518/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -13129,7 +17301,7 @@
           <t>G | 385呎 (2房)
 $993万
 $25,800/呎
-(26年-06月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr"/>
@@ -13146,7 +17318,7 @@
           <t>A | 707呎 (3房)
 $1859万
 $26,289/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -13154,7 +17326,7 @@
           <t>B | 416呎 (2房)
 $975万
 $23,442/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -13162,7 +17334,7 @@
           <t>C | 414呎 (2房)
 $966万
 $23,324/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -13170,7 +17342,7 @@
           <t>D | 624呎 (3房)
 $1632万
 $26,154/呎
-(25年-07月)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -13178,7 +17350,7 @@
           <t>E | 378呎 (2房)
 $772万
 $20,434/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -13186,7 +17358,7 @@
           <t>F | 272呎 (1房)
 $550万
 $20,202/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -13194,7 +17366,7 @@
           <t>G | 385呎 (2房)
 $986万
 $25,600/呎
-(26年-06月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr"/>
@@ -13211,7 +17383,7 @@
           <t>A | 707呎 (3房)
 $1840万
 $26,031/呎
-(25年-04月)</t>
+(25年-04月-21日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -13219,7 +17391,7 @@
           <t>B | 416呎 (2房)
 $966万
 $23,209/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -13227,7 +17399,7 @@
           <t>C | 414呎 (2房)
 $1012万
 $24,454/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -13235,7 +17407,7 @@
           <t>D | 624呎 (3房)
 $1776万
 $28,462/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -13243,7 +17415,7 @@
           <t>E | 378呎 (2房)
 $751万
 $19,876/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -13251,7 +17423,7 @@
           <t>F | 272呎 (1房)
 $536万
 $19,688/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -13259,7 +17431,7 @@
           <t>G | 385呎 (2房)
 $828万
 $21,501/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr"/>
@@ -13276,7 +17448,7 @@
           <t>A | 707呎 (3房)
 $1875万
 $26,518/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -13284,7 +17456,7 @@
           <t>B | 416呎 (2房)
 $967万
 $23,252/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -13292,7 +17464,7 @@
           <t>C | 414呎 (2房)
 $958万
 $23,143/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -13300,7 +17472,7 @@
           <t>D | 624呎 (3房)
 $1600万
 $25,636/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -13308,7 +17480,7 @@
           <t>E | 378呎 (2房)
 $747万
 $19,757/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -13316,7 +17488,7 @@
           <t>F | 272呎 (1房)
 $532万
 $19,570/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -13324,7 +17496,7 @@
           <t>G | 385呎 (2房)
 $776万
 $20,166/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr"/>
@@ -13341,7 +17513,7 @@
           <t>A | 707呎 (3房)
 $1778万
 $25,146/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -13349,7 +17521,7 @@
           <t>B | 416呎 (2房)
 $942万
 $22,651/呎
-(24年-06月)</t>
+(24年-06月-10日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -13357,7 +17529,7 @@
           <t>C | 414呎 (2房)
 $933万
 $22,536/呎
-(24年-06月)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -13365,7 +17537,7 @@
           <t>D | 624呎 (3房)
 $1661万
 $26,622/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -13373,7 +17545,7 @@
           <t>E | 378呎 (2房)
 $712万
 $18,844/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -13381,7 +17553,7 @@
           <t>F | 272呎 (1房)
 $557万
 $20,463/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -13389,7 +17561,7 @@
           <t>G | 385呎 (2房)
 $796万
 $20,662/呎
-(24年-06月)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr"/>
@@ -13406,7 +17578,7 @@
           <t>A | 707呎 (3房)
 $1704万
 $24,095/呎
-(25年-03月)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -13414,7 +17586,7 @@
           <t>B | 416呎 (2房)
 $979万
 $23,531/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -13422,7 +17594,7 @@
           <t>C | 414呎 (2房)
 $936万
 $22,621/呎
-(24年-12月)</t>
+(24年-12月-01日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -13430,7 +17602,7 @@
           <t>D | 624呎 (3房)
 $1534万
 $24,583/呎
-(25年-05月)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -13438,7 +17610,7 @@
           <t>E | 378呎 (2房)
 $709万
 $18,751/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -13446,7 +17618,7 @@
           <t>F | 272呎 (1房)
 $554万
 $20,357/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -13454,7 +17626,7 @@
           <t>G | 385呎 (2房)
 $789万
 $20,483/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr"/>
@@ -13471,7 +17643,7 @@
           <t>A | 707呎 (3房)
 $1923万
 $27,200/呎
-(26年-06月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -13479,7 +17651,7 @@
           <t>B | 416呎 (2房)
 $927万
 $22,293/呎
-(24年-06月)</t>
+(24年-06月-24日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -13487,7 +17659,7 @@
           <t>C | 414呎 (2房)
 $929万
 $22,444/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -13495,7 +17667,7 @@
           <t>D | 624呎 (3房)
 $1522万
 $24,391/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -13503,7 +17675,7 @@
           <t>E | 378呎 (2房)
 $705万
 $18,661/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -13511,7 +17683,7 @@
           <t>F | 272呎 (1房)
 $551万
 $20,261/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -13519,7 +17691,7 @@
           <t>G | 385呎 (2房)
 $738万
 $19,171/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr"/>
@@ -13536,7 +17708,7 @@
           <t>A | 707呎 (2房)
 $1889万
 $26,716/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -13544,7 +17716,7 @@
           <t>B | 416呎 (2房)
 $938万
 $22,555/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -13552,7 +17724,7 @@
           <t>C | 414呎 (2房)
 $929万
 $22,444/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -13560,7 +17732,7 @@
           <t>D | 624呎 (3房)
 $1693万
 $27,130/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -13568,7 +17740,7 @@
           <t>E | 378呎 (2房)
 $705万
 $18,661/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -13576,7 +17748,7 @@
           <t>F | 272呎 (1房)
 $551万
 $20,261/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -13584,7 +17756,7 @@
           <t>G | 385呎 (2房)
 $738万
 $19,171/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr"/>
@@ -13601,7 +17773,7 @@
           <t>A | 634呎 (3房)
 $1506万
 $23,759/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -13609,7 +17781,7 @@
           <t>B | 416呎 (2房)
 $893万
 $21,466/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -13617,7 +17789,7 @@
           <t>C | 414呎 (2房)
 $856万
 $20,679/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -13625,7 +17797,7 @@
           <t>D | 624呎 (3房)
 $1580万
 $25,321/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -13633,7 +17805,7 @@
           <t>E | 278呎 (1房)
 $527万
 $18,942/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -13641,7 +17813,7 @@
           <t>F | 269呎 (1房)
 $517万
 $19,216/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -13649,7 +17821,7 @@
           <t>G | 272呎 (1房)
 $680万
 $25,015/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -13657,7 +17829,7 @@
           <t>H | 269呎 (1房)
 $564万
 $20,978/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -13665,7 +17837,7 @@
           <t>J | 278呎 (1房)
 $543万
 $19,522/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -13680,7 +17852,7 @@
           <t>A | 634呎 (3房)
 $1500万
 $23,664/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -13688,7 +17860,7 @@
           <t>B | 416呎 (2房)
 $859万
 $20,654/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -13696,7 +17868,7 @@
           <t>C | 414呎 (2房)
 $903万
 $21,809/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -13704,7 +17876,7 @@
           <t>D | 624呎 (3房)
 $1621万
 $25,971/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -13712,7 +17884,7 @@
           <t>E | 278呎 (1房)
 $495万
 $17,820/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -13720,7 +17892,7 @@
           <t>F | 269呎 (1房)
 $514万
 $19,108/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -13728,7 +17900,7 @@
           <t>G | 272呎 (1房)
 $548万
 $20,129/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -13736,7 +17908,7 @@
           <t>H | 269呎 (1房)
 $531万
 $19,732/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -13744,7 +17916,7 @@
           <t>J | 278呎 (1房)
 $510万
 $18,360/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -13759,7 +17931,7 @@
           <t>A | 634呎 (3房)
 $1499万
 $23,648/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -13767,7 +17939,7 @@
           <t>B | 416呎 (2房)
 $906万
 $21,776/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -13775,7 +17947,7 @@
           <t>C | 414呎 (2房)
 $899万
 $21,722/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -13783,7 +17955,7 @@
           <t>D | 624呎 (3房)
 $1614万
 $25,870/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -13791,7 +17963,7 @@
           <t>E | 278呎 (1房)
 $494万
 $17,752/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -13799,7 +17971,7 @@
           <t>F | 269呎 (1房)
 $484万
 $17,978/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -13807,7 +17979,7 @@
           <t>G | 272呎 (1房)
 $500万
 $18,390/呎
-(24年-06月)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -13815,7 +17987,7 @@
           <t>H | 269呎 (1房)
 $560万
 $20,810/呎
-(24年-07月)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -13823,7 +17995,7 @@
           <t>J | 278呎 (1房)
 $538万
 $19,360/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -13838,7 +18010,7 @@
           <t>A | 632呎 (3房)
 $1583万
 $25,049/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -13846,7 +18018,7 @@
           <t>B | 416呎 (2房)
 $850万
 $20,428/呎
-(24年-07月)</t>
+(24年-07月-21日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -13854,7 +18026,7 @@
           <t>C | 414呎 (2房)
 $843万
 $20,372/呎
-(24年-06月)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -13862,7 +18034,7 @@
           <t>D | 624呎 (3房)
 $1543万
 $24,728/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -13870,7 +18042,7 @@
           <t>E | 278呎 (1房)
 $490万
 $17,633/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -13878,7 +18050,7 @@
           <t>F | 269呎 (1房)
 $508万
 $18,866/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -13886,7 +18058,7 @@
           <t>G | 272呎 (1房)
 $497万
 $18,261/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -13894,7 +18066,7 @@
           <t>H | 232呎 (1房)
 $647万
 $27,892/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -13902,7 +18074,7 @@
           <t>J | 240呎 (1房)
 $662万
 $27,600/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -13988,22 +18160,22 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
@@ -14068,9 +18240,9 @@
       <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 1452呎 (4+房)
+招标单位
 -
--
-(待售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -14080,7 +18252,7 @@
           <t>D | 378呎 (2房)
 $890万
 $23,548/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -14088,7 +18260,7 @@
           <t>E | 377呎 (2房)
 $885万
 $23,475/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -14096,7 +18268,7 @@
           <t>F | 377呎 (2房)
 $881万
 $23,366/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -14104,7 +18276,7 @@
           <t>G | 272呎 (1房)
 $684万
 $25,129/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -14112,7 +18284,7 @@
           <t>H | 382呎 (2房)
 $862万
 $22,555/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr"/>
@@ -14128,7 +18300,7 @@
           <t>A | 1056呎 (3房)
 $3726万
 $35,280/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -14137,7 +18309,7 @@
           <t>C | 423呎 (2房)
 $1027万
 $24,272/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -14145,7 +18317,7 @@
           <t>D | 380呎 (2房)
 $861万
 $22,650/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -14153,7 +18325,7 @@
           <t>E | 377呎 (2房)
 $871万
 $23,106/呎
-(24年-12月)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -14161,7 +18333,7 @@
           <t>F | 377呎 (2房)
 $867万
 $22,995/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -14169,7 +18341,7 @@
           <t>G | 272呎 (1房)
 $597万
 $21,952/呎
-(24年-09月)</t>
+(24年-09月-01日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -14177,7 +18349,7 @@
           <t>H | 382呎 (2房)
 $850万
 $22,264/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr"/>
@@ -14193,7 +18365,7 @@
           <t>A | 569呎 (3房)
 $1450万
 $25,485/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -14201,7 +18373,7 @@
           <t>B | 415呎 (2房)
 $985万
 $23,740/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -14209,7 +18381,7 @@
           <t>C | 423呎 (2房)
 $1014万
 $23,960/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -14217,7 +18389,7 @@
           <t>D | 382呎 (2房)
 $847万
 $22,162/呎
-(25年-05月)</t>
+(25年-05月-25日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -14225,7 +18397,7 @@
           <t>E | 377呎 (2房)
 $852万
 $22,613/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -14233,7 +18405,7 @@
           <t>F | 377呎 (2房)
 $898万
 $23,812/呎
-(24年-08月)</t>
+(24年-08月-26日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -14241,7 +18413,7 @@
           <t>G | 272呎 (1房)
 $620万
 $22,794/呎
-(24年-09月)</t>
+(24年-09月-08日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -14249,7 +18421,7 @@
           <t>H | 382呎 (2房)
 $872万
 $22,835/呎
-(24年-12月)</t>
+(24年-12月-15日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr"/>
@@ -14265,7 +18437,7 @@
           <t>A | 569呎 (3房)
 $1416万
 $24,877/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -14273,7 +18445,7 @@
           <t>B | 415呎 (2房)
 $998万
 $24,051/呎
-(25年-07月)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -14281,7 +18453,7 @@
           <t>C | 423呎 (2房)
 $1004万
 $23,723/呎
-(25年-08月)</t>
+(25年-08月-03日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -14289,7 +18461,7 @@
           <t>D | 382呎 (2房)
 $830万
 $21,728/呎
-(25年-01月)</t>
+(25年-01月-13日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -14297,7 +18469,7 @@
           <t>E | 377呎 (2房)
 $836万
 $22,170/呎
-(24年-08月)</t>
+(24年-08月-22日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -14305,7 +18477,7 @@
           <t>F | 377呎 (2房)
 $832万
 $22,064/呎
-(24年-10月)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -14313,7 +18485,7 @@
           <t>G | 272呎 (1房)
 $579万
 $21,294/呎
-(24年-07月)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -14321,7 +18493,7 @@
           <t>H | 382呎 (2房)
 $843万
 $22,065/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr"/>
@@ -14337,7 +18509,7 @@
           <t>A | 569呎 (3房)
 $1423万
 $25,014/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -14345,7 +18517,7 @@
           <t>B | 415呎 (2房)
 $932万
 $22,470/呎
-(25年-02月)</t>
+(25年-02月-03日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -14353,7 +18525,7 @@
           <t>C | 423呎 (2房)
 $960万
 $22,686/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -14361,7 +18533,7 @@
           <t>D | 382呎 (2房)
 $801万
 $20,974/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -14369,7 +18541,7 @@
           <t>E | 377呎 (2房)
 $844万
 $22,393/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -14377,7 +18549,7 @@
           <t>F | 377呎 (2房)
 $840万
 $22,286/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -14385,7 +18557,7 @@
           <t>G | 272呎 (1房)
 $559万
 $20,544/呎
-(24年-07月)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -14393,7 +18565,7 @@
           <t>H | 382呎 (2房)
 $814万
 $21,301/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr"/>
@@ -14409,7 +18581,7 @@
           <t>A | 569呎 (3房)
 $1446万
 $25,422/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -14417,7 +18589,7 @@
           <t>B | 415呎 (2房)
 $958万
 $23,087/呎
-(25年-01月)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -14425,7 +18597,7 @@
           <t>C | 423呎 (2房)
 $953万
 $22,532/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -14433,7 +18605,7 @@
           <t>D | 382呎 (2房)
 $833万
 $21,804/呎
-(24年-07月)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -14441,7 +18613,7 @@
           <t>E | 377呎 (2房)
 $838万
 $22,241/呎
-(24年-07月)</t>
+(24年-07月-09日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -14449,7 +18621,7 @@
           <t>F | 377呎 (2房)
 $834万
 $22,133/呎
-(24年-07月)</t>
+(24年-07月-14日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -14457,7 +18629,7 @@
           <t>G | 272呎 (1房)
 $588万
 $21,625/呎
-(24年-07月)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -14465,7 +18637,7 @@
           <t>H | 382呎 (2房)
 $846万
 $22,157/呎
-(24年-07月)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr"/>
@@ -14481,7 +18653,7 @@
           <t>A | 569呎 (3房)
 $1404万
 $24,678/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -14489,7 +18661,7 @@
           <t>B | 415呎 (2房)
 $941万
 $22,672/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -14497,7 +18669,7 @@
           <t>C | 423呎 (2房)
 $947万
 $22,381/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -14505,7 +18677,7 @@
           <t>D | 382呎 (2房)
 $781万
 $20,450/呎
-(24年-07月)</t>
+(24年-07月-22日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -14513,7 +18685,7 @@
           <t>E | 377呎 (2房)
 $833万
 $22,093/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -14521,7 +18693,7 @@
           <t>F | 377呎 (2房)
 $828万
 $21,976/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -14529,7 +18701,7 @@
           <t>G | 272呎 (1房)
 $705万
 $25,919/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -14537,7 +18709,7 @@
           <t>H | 382呎 (2房)
 $804万
 $21,052/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr"/>
@@ -14553,7 +18725,7 @@
           <t>A | 569呎 (3房)
 $1394万
 $24,504/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -14561,7 +18733,7 @@
           <t>B | 415呎 (2房)
 $913万
 $22,005/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -14569,7 +18741,7 @@
           <t>C | 423呎 (2房)
 $940万
 $22,222/呎
-(25年-05月)</t>
+(25年-05月-25日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -14577,7 +18749,7 @@
           <t>D | 382呎 (2房)
 $776万
 $20,306/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -14585,7 +18757,7 @@
           <t>E | 377呎 (2房)
 $781万
 $20,721/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -14593,7 +18765,7 @@
           <t>F | 377呎 (2房)
 $823万
 $21,825/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -14601,7 +18773,7 @@
           <t>G | 272呎 (1房)
 $581万
 $21,375/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -14609,7 +18781,7 @@
           <t>H | 382呎 (2房)
 $799万
 $20,927/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr"/>
@@ -14625,7 +18797,7 @@
           <t>A | 569呎 (3房)
 $1385万
 $24,334/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -14633,7 +18805,7 @@
           <t>B | 415呎 (2房)
 $907万
 $21,848/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -14641,7 +18813,7 @@
           <t>C | 423呎 (2房)
 $934万
 $22,073/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -14649,7 +18821,7 @@
           <t>D | 382呎 (2房)
 $816万
 $21,351/呎
-(24年-06月)</t>
+(24年-06月-16日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -14657,7 +18829,7 @@
           <t>E | 377呎 (2房)
 $821万
 $21,785/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -14665,7 +18837,7 @@
           <t>F | 377呎 (2房)
 $772万
 $20,472/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -14673,7 +18845,7 @@
           <t>G | 272呎 (1房)
 $546万
 $20,059/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -14681,7 +18853,7 @@
           <t>H | 382呎 (2房)
 $813万
 $21,288/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr"/>
@@ -14697,7 +18869,7 @@
           <t>A | 569呎 (3房)
 $1260万
 $22,135/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -14705,7 +18877,7 @@
           <t>B | 415呎 (2房)
 $901万
 $21,704/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -14713,7 +18885,7 @@
           <t>C | 423呎 (2房)
 $905万
 $21,385/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -14721,7 +18893,7 @@
           <t>D | 382呎 (2房)
 $730万
 $19,097/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -14729,7 +18901,7 @@
           <t>E | 377呎 (2房)
 $735万
 $19,485/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -14737,7 +18909,7 @@
           <t>F | 377呎 (2房)
 $732万
 $19,430/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -14745,7 +18917,7 @@
           <t>G | 272呎 (1房)
 $527万
 $19,375/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -14753,7 +18925,7 @@
           <t>H | 382呎 (2房)
 $742万
 $19,419/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr"/>
@@ -14769,7 +18941,7 @@
           <t>A | 569呎 (3房)
 $1330万
 $23,374/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -14777,7 +18949,7 @@
           <t>B | 415呎 (2房)
 $896万
 $21,578/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -14785,7 +18957,7 @@
           <t>C | 423呎 (2房)
 $910万
 $21,511/呎
-(24年-12月)</t>
+(24年-12月-01日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -14793,7 +18965,7 @@
           <t>D | 382呎 (2房)
 $725万
 $18,982/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -14801,7 +18973,7 @@
           <t>E | 377呎 (2房)
 $730万
 $19,369/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -14809,7 +18981,7 @@
           <t>F | 377呎 (2房)
 $771万
 $20,454/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -14817,7 +18989,7 @@
           <t>G | 272呎 (1房)
 $525万
 $19,287/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -14825,7 +18997,7 @@
           <t>H | 382呎 (2房)
 $782万
 $20,458/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr"/>
@@ -14841,7 +19013,7 @@
           <t>A | 569呎 (3房)
 $1322万
 $23,239/呎
-(25年-05月)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -14849,7 +19021,7 @@
           <t>B | 415呎 (2房)
 $841万
 $20,255/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -14857,7 +19029,7 @@
           <t>C | 423呎 (2房)
 $946万
 $22,376/呎
-(24年-07月)</t>
+(24年-07月-21日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -14865,7 +19037,7 @@
           <t>D | 382呎 (2房)
 $974万
 $25,500/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -14873,7 +19045,7 @@
           <t>E | 377呎 (2房)
 $726万
 $19,252/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -14881,7 +19053,7 @@
           <t>F | 377呎 (2房)
 $724万
 $19,202/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -14889,7 +19061,7 @@
           <t>G | 272呎 (1房)
 $522万
 $19,184/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -14897,7 +19069,7 @@
           <t>H | 382呎 (2房)
 $778万
 $20,359/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr"/>
@@ -14913,7 +19085,7 @@
           <t>A | 569呎 (3房)
 $1453万
 $25,543/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -14921,7 +19093,7 @@
           <t>B | 415呎 (2房)
 $841万
 $20,255/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -14929,7 +19101,7 @@
           <t>C | 423呎 (2房)
 $894万
 $21,132/呎
-(24年-06月)</t>
+(24年-06月-16日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -14937,7 +19109,7 @@
           <t>D | 382呎 (2房)
 $722万
 $18,914/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -14945,7 +19117,7 @@
           <t>E | 377呎 (2房)
 $768万
 $20,385/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -14953,7 +19125,7 @@
           <t>F | 377呎 (2房)
 $724万
 $19,202/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -14961,7 +19133,7 @@
           <t>G | 272呎 (1房)
 $552万
 $20,312/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -14969,7 +19141,7 @@
           <t>H | 382呎 (2房)
 $734万
 $19,228/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr"/>
@@ -14985,7 +19157,7 @@
           <t>A | 545呎 (3房)
 $1159万
 $21,261/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -14993,7 +19165,7 @@
           <t>B | 418呎 (2房)
 $825万
 $19,744/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -15001,7 +19173,7 @@
           <t>C | 423呎 (2房)
 $835万
 $19,740/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -15009,7 +19181,7 @@
           <t>D | 277呎 (1房)
 $511万
 $18,437/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -15017,7 +19189,7 @@
           <t>E | 269呎 (1房)
 $568万
 $21,104/呎
-(24年-08月)</t>
+(24年-08月-22日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -15025,7 +19197,7 @@
           <t>F | 270呎 (1房)
 $507万
 $18,785/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -15033,7 +19205,7 @@
           <t>G | 270呎 (1房)
 $505万
 $18,715/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -15041,7 +19213,7 @@
           <t>H | 272呎 (1房)
 $495万
 $18,188/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -15049,7 +19221,7 @@
           <t>J | 277呎 (1房)
 $538万
 $19,404/呎
-(24年-06月)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -15064,7 +19236,7 @@
           <t>A | 545呎 (3房)
 $1222万
 $22,424/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -15072,7 +19244,7 @@
           <t>B | 418呎 (2房)
 $870万
 $20,818/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -15080,7 +19252,7 @@
           <t>C | 423呎 (2房)
 $881万
 $20,820/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -15088,7 +19260,7 @@
           <t>D | 277呎 (1房)
 $538万
 $19,440/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -15096,7 +19268,7 @@
           <t>E | 269呎 (1房)
 $534万
 $19,862/呎
-(24年-08月)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -15104,7 +19276,7 @@
           <t>F | 270呎 (1房)
 $535万
 $19,811/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -15112,7 +19284,7 @@
           <t>G | 270呎 (1房)
 $533万
 $19,741/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -15120,7 +19292,7 @@
           <t>H | 272呎 (1房)
 $492万
 $18,099/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -15128,7 +19300,7 @@
           <t>J | 277呎 (1房)
 $535万
 $19,303/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
     </row>
@@ -15143,7 +19315,7 @@
           <t>A | 545呎 (3房)
 $1150万
 $21,092/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -15151,7 +19323,7 @@
           <t>B | 418呎 (2房)
 $819万
 $19,584/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -15159,7 +19331,7 @@
           <t>C | 423呎 (2房)
 $828万
 $19,586/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -15167,7 +19339,7 @@
           <t>D | 277呎 (1房)
 $536万
 $19,365/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -15175,7 +19347,7 @@
           <t>E | 269呎 (1房)
 $563万
 $20,933/呎
-(24年-09月)</t>
+(24年-09月-08日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -15183,7 +19355,7 @@
           <t>F | 270呎 (1房)
 $503万
 $18,637/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -15191,7 +19363,7 @@
           <t>G | 270呎 (1房)
 $501万
 $18,567/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -15199,7 +19371,7 @@
           <t>H | 272呎 (1房)
 $519万
 $19,070/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -15207,7 +19379,7 @@
           <t>J | 277呎 (1房)
 $532万
 $19,209/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -15222,7 +19394,7 @@
           <t>A | 508呎 (3房)
 $1432万
 $28,181/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -15230,7 +19402,7 @@
           <t>B | 380呎 (2房)
 $1096万
 $28,850/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -15238,7 +19410,7 @@
           <t>C | 385呎 (2房)
 $1110万
 $28,844/呎
-(25年-07月)</t>
+(25年-07月-20日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -15246,7 +19418,7 @@
           <t>D | 239呎 (1房)
 $638万
 $26,690/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -15254,7 +19426,7 @@
           <t>E | 232呎 (1房)
 $688万
 $29,651/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -15262,7 +19434,7 @@
           <t>F | 232呎 (1房)
 $618万
 $26,638/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -15270,7 +19442,7 @@
           <t>G | 232呎 (1房)
 $650万
 $28,030/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -15278,7 +19450,7 @@
           <t>H | 272呎 (1房)
 $486万
 $17,871/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -15286,7 +19458,7 @@
           <t>J | 277呎 (1房)
 $499万
 $18,000/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-佐敦-高临.xlsx
+++ b/files/九龙-佐敦-高临.xlsx
@@ -122,7 +122,8 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -267,7 +268,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8633,7 +8634,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -18155,12 +18156,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -18242,7 +18243,7 @@
           <t>A | 1452呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
